--- a/guest_registration_forms/020_simple_guest_list_form--guest_registration_forms.xlsx
+++ b/guest_registration_forms/020_simple_guest_list_form--guest_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
     <col width="35" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -574,11 +574,7 @@
           <t>Email</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Enter the guest's email address</t>
-        </is>
-      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>no</t>
@@ -841,17 +837,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>first_name_confirmation_2</t>
+          <t>first_name_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>First Name 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -864,17 +860,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>last_name_confirmation_2</t>
+          <t>last_name_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Last Name 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -892,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>email_confirmation_2</t>
+          <t>email_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Email 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -915,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>phone_confirmation_2</t>
+          <t>phone_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Phone 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -938,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>date_of_attendance_confirmation_2</t>
+          <t>date_of_attendance_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Date of Attendance</t>
+          <t>Date Of Attendance 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -961,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>time_of_attendance_confirmation_2</t>
+          <t>time_of_attendance_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Time of Attendance</t>
+          <t>Time Of Attendance 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -984,108 +980,16 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>note_confirmation_2</t>
+          <t>note_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>Note 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>first_name_2</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>First Name</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>last_name_2</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Last Name</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>email_2</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>phone_2</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1102,12 +1006,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1135,12 +1039,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'john'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'John'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1056,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'jane'}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Jane'}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1169,12 +1073,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1186,80 +1090,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>first_name_confirmation_2_choices</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>first_name_confirmation_2_choices</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>last_name_confirmation_2_choices</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>last_name_confirmation_2_choices</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
